--- a/SWAFDP.xlsx
+++ b/SWAFDP.xlsx
@@ -43,7 +43,7 @@
     <t>20142495</t>
   </si>
   <si>
-    <t>INDOMARET AIR MIN 1L</t>
+    <t>IDM AIR MINE BTL 1 L</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>

--- a/SWAFDP.xlsx
+++ b/SWAFDP.xlsx
@@ -19,7 +19,7 @@
     <t>10004336</t>
   </si>
   <si>
-    <t>INDOMARET AIR MIN600</t>
+    <t>IDM MINERAL 600 ML</t>
   </si>
   <si>
     <t>SWAFDP</t>
